--- a/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0002.xlsx
+++ b/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0002.xlsx
@@ -1892,17 +1892,17 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Att undvika val</t>
+          <t>Att vinna varje omröstning</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Att förbjuda debatt</t>
+          <t>Att undvika samarbete</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Att alltid vinna</t>
+          <t>Att följa order utan debatt</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1949,17 +1949,17 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Arbetslösheten försvann</t>
+          <t>Arbetslösheten minskade</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Skatter togs bort</t>
+          <t>Skatteintäkterna ökade</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Mat fanns i överflöd</t>
+          <t>Konsumtionen ökade</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Det var bara brist på bilar</t>
+          <t>Det var främst brist på arbete och inkomster</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Det fanns aldrig brist</t>
+          <t>Det var brist på kredit och investeringar</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Bristen gällde bara guld</t>
+          <t>Bristen gällde främst exportinkomster</t>
         </is>
       </c>
       <c r="G12" s="14" t="n">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Miljörörelsen</t>
+          <t>Kommunister</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Kommunalråd</t>
+          <t>Liberaler</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Fackföreningar</t>
+          <t>Socialdemokrater</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Den lovade att avskaffa mat</t>
+          <t>Den lovade jobb och ordning</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Den lovade att stoppa handel</t>
+          <t>Den lovade ekonomisk återhämtning</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Den lovade att avskaffa skolor</t>
+          <t>Den lovade starkare statlig kontroll</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>De avskaffade pengar</t>
+          <t>De införde mer protektionism</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>De försvann</t>
+          <t>De fick instabila koalitionsregeringar</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>De blev kolonier i Afrika</t>
+          <t>De stärkte statens kontroll över ekonomin</t>
         </is>
       </c>
       <c r="G16" s="14" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Finland blev en diktatur</t>
+          <t>Finland blev en auktoritär stat</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Finland upphörde</t>
+          <t>Finland avskaffade fria val</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Finland blev en koloni</t>
+          <t>Finland styrdes av en militärjunta</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Våren 1918</t>
+          <t>Våren 1939</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Våren 1945</t>
+          <t>Vintern 1940</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Vintern 1991</t>
+          <t>Sommaren 1941</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Finland ville bli del av Sovjet</t>
+          <t>Sovjet ville utvidga sitt inflytande i Norden</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>Finland bad om invasion</t>
+          <t>Sovjet ville få kontroll över hela Östersjöområdet</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Finland hade inga gränser</t>
+          <t>Sovjet ville stoppa Finlands närmande till väst</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Koreakriget</t>
+          <t>Finska kriget</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Krimkriget</t>
+          <t>Fortsättningskriget</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Balkankriget</t>
+          <t>Lapplandskriget</t>
         </is>
       </c>
       <c r="G20" s="14" t="n">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>De splittrades mer än 1918</t>
+          <t>Motsättningarna dämpades men fanns kvar</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>De flyttade alla utomlands</t>
+          <t>Många var oeniga om hur man skulle försvara landet</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>De slutade arbeta</t>
+          <t>Den politiska enigheten uteblev</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Att kriget var oviktigt</t>
+          <t>Att hemmafronten och försörjningen var viktiga</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Att Finland skulle ge upp direkt</t>
+          <t>Att uthållighet och sammanhållning krävdes</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Att allt var som vanligt</t>
+          <t>Att snabb fred var nödvändig</t>
         </is>
       </c>
       <c r="G22" s="14" t="n">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Erövra Norge</t>
+          <t>Ta tillbaka Karelen</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>Avskaffa val</t>
+          <t>Tvinga fram fred på egna villkor</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Bli del av Tyskland</t>
+          <t>Skydda huvudstaden</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Vinterkriget och Vietnamkriget</t>
+          <t>Vinterkriget och Lapplandskriget</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Fortsättningskriget och Koreakriget</t>
+          <t>Fortsättningskriget och Lapplandskriget</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Lapplandskriget och Gulfkriget</t>
+          <t>Vinterkriget och inbördeskriget</t>
         </is>
       </c>
       <c r="G24" s="14" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Krimkriget</t>
+          <t>Vinterkriget</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>Boerkriget</t>
+          <t>Fortsättningskriget</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Falklandskriget</t>
+          <t>Inbördeskriget 1918</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
@@ -2918,17 +2918,17 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Allt språk</t>
+          <t>Politisk självständighet</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Alla sjöar</t>
+          <t>Rätten att ha en armé</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>All industri</t>
+          <t>Sitt officiella språk</t>
         </is>
       </c>
       <c r="G28" s="14" t="n">
